--- a/DateBase/orders/Nhat 48_2026-4-19.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-19.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>601_康乃馨大红_red_undefined_20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121210121710411190</v>
+        <v>01212101217104111910</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-4-19.xlsx
+++ b/DateBase/orders/Nhat 48_2026-4-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,39 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>834_海芋黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +611,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01212101217104111910</v>
+        <v>012121012171041119105415</v>
       </c>
     </row>
   </sheetData>
